--- a/public/Validation.xlsx
+++ b/public/Validation.xlsx
@@ -5719,7 +5719,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E380"/>
+  <dimension ref="A1:E382"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6290,13 +6290,13 @@
         <v>01 ADD ONS</v>
       </c>
       <c r="C34" t="str">
-        <v>ADD ONS SYRUPS</v>
+        <v>ADD ONS MILK</v>
       </c>
       <c r="D34" t="str">
-        <v>Brown Sugar Syrup</v>
+        <v>Dairy Milk</v>
       </c>
       <c r="E34">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35">
@@ -6310,7 +6310,7 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D35" t="str">
-        <v>Burnt Vanilla Syrup</v>
+        <v>Brown Sugar Syrup</v>
       </c>
       <c r="E35">
         <v>30</v>
@@ -6327,7 +6327,7 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D36" t="str">
-        <v>Butterscotch Syrup</v>
+        <v>Burnt Vanilla Syrup</v>
       </c>
       <c r="E36">
         <v>30</v>
@@ -6344,10 +6344,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D37" t="str">
-        <v>Caramelized Banana Syrup</v>
+        <v>Butterscotch Syrup</v>
       </c>
       <c r="E37">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
@@ -6361,10 +6361,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D38" t="str">
-        <v>French Vanilla Syrup</v>
+        <v>Caramelized Banana Syrup</v>
       </c>
       <c r="E38">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
@@ -6378,10 +6378,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D39" t="str">
-        <v>Honey Syrup</v>
+        <v>French Vanilla Syrup</v>
       </c>
       <c r="E39">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
@@ -6395,10 +6395,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D40" t="str">
-        <v>Peanut Butter Syrup</v>
+        <v>Honey Syrup</v>
       </c>
       <c r="E40">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41">
@@ -6412,7 +6412,7 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D41" t="str">
-        <v>Salted Caramel Syrup</v>
+        <v>Peanut Butter Syrup</v>
       </c>
       <c r="E41">
         <v>30</v>
@@ -6429,7 +6429,7 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D42" t="str">
-        <v>Signature Mocha Syrup</v>
+        <v>Salted Caramel Syrup</v>
       </c>
       <c r="E42">
         <v>30</v>
@@ -6446,10 +6446,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D43" t="str">
-        <v>Sugar Syrup</v>
+        <v>Signature Mocha Syrup</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
@@ -6463,10 +6463,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D44" t="str">
-        <v>Spanish Latte Syrup</v>
+        <v>Sugar Syrup</v>
       </c>
       <c r="E44">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -6480,10 +6480,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D45" t="str">
-        <v>Strawberry Puree</v>
+        <v>Spanish Latte Syrup</v>
       </c>
       <c r="E45">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
@@ -6497,10 +6497,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D46" t="str">
-        <v>White Chocolate Mocha Syrup</v>
+        <v>Strawberry Puree</v>
       </c>
       <c r="E46">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47">
@@ -6511,13 +6511,13 @@
         <v>01 ADD ONS</v>
       </c>
       <c r="C47" t="str">
-        <v>ADD ONS FOAM</v>
+        <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D47" t="str">
-        <v>Black Sesame Cold Foam</v>
+        <v>White Chocolate Mocha Syrup</v>
       </c>
       <c r="E47">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
@@ -6531,10 +6531,10 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D48" t="str">
-        <v>Chocolate Foam</v>
+        <v>Black Sesame Cold Foam</v>
       </c>
       <c r="E48">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49">
@@ -6548,10 +6548,10 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D49" t="str">
-        <v>Hojicha Cold Foam</v>
+        <v>Chocolate Foam</v>
       </c>
       <c r="E49">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
@@ -6565,7 +6565,7 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D50" t="str">
-        <v>Malted Chocolate Foam</v>
+        <v>Hojicha Cold Foam</v>
       </c>
       <c r="E50">
         <v>50</v>
@@ -6582,7 +6582,7 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D51" t="str">
-        <v>Matcha Cream Foam</v>
+        <v>Malted Chocolate Foam</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -6599,7 +6599,7 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D52" t="str">
-        <v>Rock Salt Cheese Foam</v>
+        <v>Matcha Cream Foam</v>
       </c>
       <c r="E52">
         <v>50</v>
@@ -6616,10 +6616,10 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D53" t="str">
-        <v>Salted Caramel Foam</v>
+        <v>Rock Salt Cheese Foam</v>
       </c>
       <c r="E53">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54">
@@ -6633,10 +6633,10 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D54" t="str">
-        <v>Salted Cream Foam</v>
+        <v>Salted Caramel Foam</v>
       </c>
       <c r="E54">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55">
@@ -6650,7 +6650,7 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D55" t="str">
-        <v>Strawberry Cream Foam</v>
+        <v>Salted Cream Foam</v>
       </c>
       <c r="E55">
         <v>50</v>
@@ -6658,19 +6658,19 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ICED</v>
+        <v>ADD ONS</v>
       </c>
       <c r="B56" t="str">
-        <v>02 DOT CLASSICS</v>
+        <v>01 ADD ONS</v>
       </c>
       <c r="C56" t="str">
-        <v>Americano</v>
+        <v>ADD ONS FOAM</v>
       </c>
       <c r="D56" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Strawberry Cream Foam</v>
       </c>
       <c r="E56">
-        <v>110</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57">
@@ -6684,15 +6684,15 @@
         <v>Americano</v>
       </c>
       <c r="D57" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E57">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B58" t="str">
         <v>02 DOT CLASSICS</v>
@@ -6701,10 +6701,10 @@
         <v>Americano</v>
       </c>
       <c r="D58" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E58">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59">
@@ -6718,27 +6718,27 @@
         <v>Americano</v>
       </c>
       <c r="D59" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E59">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B60" t="str">
         <v>02 DOT CLASSICS</v>
       </c>
       <c r="C60" t="str">
-        <v>Burnt Vanilla</v>
+        <v>Americano</v>
       </c>
       <c r="D60" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E60">
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61">
@@ -6752,15 +6752,15 @@
         <v>Burnt Vanilla</v>
       </c>
       <c r="D61" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E61">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B62" t="str">
         <v>02 DOT CLASSICS</v>
@@ -6769,10 +6769,10 @@
         <v>Burnt Vanilla</v>
       </c>
       <c r="D62" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E62">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63">
@@ -6786,27 +6786,27 @@
         <v>Burnt Vanilla</v>
       </c>
       <c r="D63" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E63">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B64" t="str">
         <v>02 DOT CLASSICS</v>
       </c>
       <c r="C64" t="str">
-        <v>Butterscotch</v>
+        <v>Burnt Vanilla</v>
       </c>
       <c r="D64" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E64">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65">
@@ -6820,15 +6820,15 @@
         <v>Butterscotch</v>
       </c>
       <c r="D65" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E65">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B66" t="str">
         <v>02 DOT CLASSICS</v>
@@ -6837,10 +6837,10 @@
         <v>Butterscotch</v>
       </c>
       <c r="D66" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E66">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="67">
@@ -6854,27 +6854,27 @@
         <v>Butterscotch</v>
       </c>
       <c r="D67" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E67">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B68" t="str">
         <v>02 DOT CLASSICS</v>
       </c>
       <c r="C68" t="str">
-        <v>Cold Brew</v>
+        <v>Butterscotch</v>
       </c>
       <c r="D68" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E68">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69">
@@ -6888,10 +6888,10 @@
         <v>Cold Brew</v>
       </c>
       <c r="D69" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E69">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="70">
@@ -6902,13 +6902,13 @@
         <v>02 DOT CLASSICS</v>
       </c>
       <c r="C70" t="str">
-        <v>Dirty Matcha</v>
+        <v>Cold Brew</v>
       </c>
       <c r="D70" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E70">
-        <v>180</v>
+        <v>130</v>
       </c>
     </row>
     <row r="71">
@@ -6922,15 +6922,15 @@
         <v>Dirty Matcha</v>
       </c>
       <c r="D71" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E71">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B72" t="str">
         <v>02 DOT CLASSICS</v>
@@ -6939,10 +6939,10 @@
         <v>Dirty Matcha</v>
       </c>
       <c r="D72" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E72">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="73">
@@ -6956,27 +6956,27 @@
         <v>Dirty Matcha</v>
       </c>
       <c r="D73" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E73">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B74" t="str">
         <v>02 DOT CLASSICS</v>
       </c>
       <c r="C74" t="str">
-        <v>Latte</v>
+        <v>Dirty Matcha</v>
       </c>
       <c r="D74" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E74">
-        <v>130</v>
+        <v>190</v>
       </c>
     </row>
     <row r="75">
@@ -6990,15 +6990,15 @@
         <v>Latte</v>
       </c>
       <c r="D75" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E75">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B76" t="str">
         <v>02 DOT CLASSICS</v>
@@ -7007,10 +7007,10 @@
         <v>Latte</v>
       </c>
       <c r="D76" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E76">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77">
@@ -7024,27 +7024,27 @@
         <v>Latte</v>
       </c>
       <c r="D77" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E77">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B78" t="str">
         <v>02 DOT CLASSICS</v>
       </c>
       <c r="C78" t="str">
-        <v>Matcha</v>
+        <v>Latte</v>
       </c>
       <c r="D78" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E78">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79">
@@ -7058,15 +7058,15 @@
         <v>Matcha</v>
       </c>
       <c r="D79" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E79">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B80" t="str">
         <v>02 DOT CLASSICS</v>
@@ -7075,10 +7075,10 @@
         <v>Matcha</v>
       </c>
       <c r="D80" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E80">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81">
@@ -7092,27 +7092,27 @@
         <v>Matcha</v>
       </c>
       <c r="D81" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E81">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B82" t="str">
         <v>02 DOT CLASSICS</v>
       </c>
       <c r="C82" t="str">
-        <v>Salted Caramel</v>
+        <v>Matcha</v>
       </c>
       <c r="D82" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E82">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83">
@@ -7126,15 +7126,15 @@
         <v>Salted Caramel</v>
       </c>
       <c r="D83" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E83">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B84" t="str">
         <v>02 DOT CLASSICS</v>
@@ -7143,10 +7143,10 @@
         <v>Salted Caramel</v>
       </c>
       <c r="D84" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E84">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="85">
@@ -7160,27 +7160,27 @@
         <v>Salted Caramel</v>
       </c>
       <c r="D85" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E85">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B86" t="str">
         <v>02 DOT CLASSICS</v>
       </c>
       <c r="C86" t="str">
-        <v>Signature Mocha</v>
+        <v>Salted Caramel</v>
       </c>
       <c r="D86" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E86">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="87">
@@ -7194,15 +7194,15 @@
         <v>Signature Mocha</v>
       </c>
       <c r="D87" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E87">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B88" t="str">
         <v>02 DOT CLASSICS</v>
@@ -7211,10 +7211,10 @@
         <v>Signature Mocha</v>
       </c>
       <c r="D88" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E88">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="89">
@@ -7228,27 +7228,27 @@
         <v>Signature Mocha</v>
       </c>
       <c r="D89" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E89">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B90" t="str">
         <v>02 DOT CLASSICS</v>
       </c>
       <c r="C90" t="str">
-        <v>Spanish Latte</v>
+        <v>Signature Mocha</v>
       </c>
       <c r="D90" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E90">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="91">
@@ -7262,15 +7262,15 @@
         <v>Spanish Latte</v>
       </c>
       <c r="D91" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E91">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B92" t="str">
         <v>02 DOT CLASSICS</v>
@@ -7279,10 +7279,10 @@
         <v>Spanish Latte</v>
       </c>
       <c r="D92" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E92">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="93">
@@ -7296,27 +7296,27 @@
         <v>Spanish Latte</v>
       </c>
       <c r="D93" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E93">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B94" t="str">
         <v>02 DOT CLASSICS</v>
       </c>
       <c r="C94" t="str">
-        <v>White Chocolate Mocha</v>
+        <v>Spanish Latte</v>
       </c>
       <c r="D94" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E94">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="95">
@@ -7330,15 +7330,15 @@
         <v>White Chocolate Mocha</v>
       </c>
       <c r="D95" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E95">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B96" t="str">
         <v>02 DOT CLASSICS</v>
@@ -7347,10 +7347,10 @@
         <v>White Chocolate Mocha</v>
       </c>
       <c r="D96" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E96">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="97">
@@ -7364,27 +7364,27 @@
         <v>White Chocolate Mocha</v>
       </c>
       <c r="D97" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E97">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B98" t="str">
-        <v>03 DOT SIGNATURES</v>
+        <v>02 DOT CLASSICS</v>
       </c>
       <c r="C98" t="str">
-        <v>Black Sesame Hojicha Latte</v>
+        <v>White Chocolate Mocha</v>
       </c>
       <c r="D98" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E98">
-        <v>220</v>
+        <v>160</v>
       </c>
     </row>
     <row r="99">
@@ -7398,10 +7398,10 @@
         <v>Black Sesame Hojicha Latte</v>
       </c>
       <c r="D99" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E99">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="100">
@@ -7412,13 +7412,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C100" t="str">
-        <v>Caramelized Banana Hojicha Latte</v>
+        <v>Black Sesame Hojicha Latte</v>
       </c>
       <c r="D100" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E100">
-        <v>190</v>
+        <v>230</v>
       </c>
     </row>
     <row r="101">
@@ -7432,10 +7432,10 @@
         <v>Caramelized Banana Hojicha Latte</v>
       </c>
       <c r="D101" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E101">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="102">
@@ -7446,13 +7446,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C102" t="str">
-        <v>Cereal Milk</v>
+        <v>Caramelized Banana Hojicha Latte</v>
       </c>
       <c r="D102" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E102">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="103">
@@ -7466,10 +7466,10 @@
         <v>Cereal Milk</v>
       </c>
       <c r="D103" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E103">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104">
@@ -7480,13 +7480,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C104" t="str">
-        <v>Chocolate Milk</v>
+        <v>Cereal Milk</v>
       </c>
       <c r="D104" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E104">
-        <v>130</v>
+        <v>160</v>
       </c>
     </row>
     <row r="105">
@@ -7500,15 +7500,15 @@
         <v>Chocolate Milk</v>
       </c>
       <c r="D105" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E105">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B106" t="str">
         <v>03 DOT SIGNATURES</v>
@@ -7517,10 +7517,10 @@
         <v>Chocolate Milk</v>
       </c>
       <c r="D106" t="str">
-        <v>Hot Regular 12oz.</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E106">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="107">
@@ -7534,27 +7534,27 @@
         <v>Chocolate Milk</v>
       </c>
       <c r="D107" t="str">
-        <v>Hot Large 16oz.</v>
+        <v>Hot Regular 12oz.</v>
       </c>
       <c r="E107">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B108" t="str">
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C108" t="str">
-        <v>Coco Americano</v>
+        <v>Chocolate Milk</v>
       </c>
       <c r="D108" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Large 16oz.</v>
       </c>
       <c r="E108">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="109">
@@ -7568,10 +7568,10 @@
         <v>Coco Americano</v>
       </c>
       <c r="D109" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E109">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="110">
@@ -7582,13 +7582,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C110" t="str">
-        <v>CocoChata</v>
+        <v>Coco Americano</v>
       </c>
       <c r="D110" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E110">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="111">
@@ -7602,10 +7602,10 @@
         <v>CocoChata</v>
       </c>
       <c r="D111" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E111">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="112">
@@ -7616,13 +7616,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C112" t="str">
-        <v>Coconut Cream Cold Brew</v>
+        <v>CocoChata</v>
       </c>
       <c r="D112" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E112">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="113">
@@ -7636,10 +7636,10 @@
         <v>Coconut Cream Cold Brew</v>
       </c>
       <c r="D113" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E113">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="114">
@@ -7650,13 +7650,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C114" t="str">
-        <v>Cookie Butter Oat Latte</v>
+        <v>Coconut Cream Cold Brew</v>
       </c>
       <c r="D114" t="str">
-        <v>Iced Regular (12oz) l Dairy</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E114">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="115">
@@ -7670,7 +7670,7 @@
         <v>Cookie Butter Oat Latte</v>
       </c>
       <c r="D115" t="str">
-        <v>Iced Regular (12oz) l Almond</v>
+        <v>Iced Regular (12oz) l Dairy</v>
       </c>
       <c r="E115">
         <v>200</v>
@@ -7687,7 +7687,7 @@
         <v>Cookie Butter Oat Latte</v>
       </c>
       <c r="D116" t="str">
-        <v>Iced Regular (12oz) l Oat</v>
+        <v>Iced Regular (12oz) l Almond</v>
       </c>
       <c r="E116">
         <v>200</v>
@@ -7704,10 +7704,10 @@
         <v>Cookie Butter Oat Latte</v>
       </c>
       <c r="D117" t="str">
-        <v>Iced Large (16oz) l Dairy</v>
+        <v>Iced Regular (12oz) l Oat</v>
       </c>
       <c r="E117">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="118">
@@ -7721,7 +7721,7 @@
         <v>Cookie Butter Oat Latte</v>
       </c>
       <c r="D118" t="str">
-        <v>Iced Large (16oz) l Almond</v>
+        <v>Iced Large (16oz) l Dairy</v>
       </c>
       <c r="E118">
         <v>210</v>
@@ -7738,7 +7738,7 @@
         <v>Cookie Butter Oat Latte</v>
       </c>
       <c r="D119" t="str">
-        <v>Iced Large (16oz) l Oat</v>
+        <v>Iced Large (16oz) l Almond</v>
       </c>
       <c r="E119">
         <v>210</v>
@@ -7752,13 +7752,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C120" t="str">
-        <v>Creamy Coco Hojicha</v>
+        <v>Cookie Butter Oat Latte</v>
       </c>
       <c r="D120" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz) l Oat</v>
       </c>
       <c r="E120">
-        <v>190</v>
+        <v>210</v>
       </c>
     </row>
     <row r="121">
@@ -7772,10 +7772,10 @@
         <v>Creamy Coco Hojicha</v>
       </c>
       <c r="D121" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E121">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="122">
@@ -7786,13 +7786,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C122" t="str">
-        <v>Creamy Coco Matcha</v>
+        <v>Creamy Coco Hojicha</v>
       </c>
       <c r="D122" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E122">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="123">
@@ -7806,10 +7806,10 @@
         <v>Creamy Coco Matcha</v>
       </c>
       <c r="D123" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E123">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="124">
@@ -7820,13 +7820,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C124" t="str">
-        <v>Dirty Cereal</v>
+        <v>Creamy Coco Matcha</v>
       </c>
       <c r="D124" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E124">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="125">
@@ -7840,10 +7840,10 @@
         <v>Dirty Cereal</v>
       </c>
       <c r="D125" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E125">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="126">
@@ -7854,13 +7854,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C126" t="str">
-        <v>Dirty Coco</v>
+        <v>Dirty Cereal</v>
       </c>
       <c r="D126" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E126">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
     <row r="127">
@@ -7874,10 +7874,10 @@
         <v>Dirty Coco</v>
       </c>
       <c r="D127" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E127">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="128">
@@ -7888,13 +7888,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C128" t="str">
-        <v>Dirty Horchata</v>
+        <v>Dirty Coco</v>
       </c>
       <c r="D128" t="str">
-        <v>Iced Regular (12oz) l Dairy</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E128">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="129">
@@ -7908,7 +7908,7 @@
         <v>Dirty Horchata</v>
       </c>
       <c r="D129" t="str">
-        <v>Iced Regular (12oz) l Almond</v>
+        <v>Iced Regular (12oz) l Dairy</v>
       </c>
       <c r="E129">
         <v>170</v>
@@ -7925,7 +7925,7 @@
         <v>Dirty Horchata</v>
       </c>
       <c r="D130" t="str">
-        <v>Iced Regular (12oz) l Oat</v>
+        <v>Iced Regular (12oz) l Almond</v>
       </c>
       <c r="E130">
         <v>170</v>
@@ -7942,10 +7942,10 @@
         <v>Dirty Horchata</v>
       </c>
       <c r="D131" t="str">
-        <v>Iced Large (16oz) l Dairy</v>
+        <v>Iced Regular (12oz) l Oat</v>
       </c>
       <c r="E131">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="132">
@@ -7959,7 +7959,7 @@
         <v>Dirty Horchata</v>
       </c>
       <c r="D132" t="str">
-        <v>Iced Large (16oz) l Almond</v>
+        <v>Iced Large (16oz) l Dairy</v>
       </c>
       <c r="E132">
         <v>180</v>
@@ -7976,7 +7976,7 @@
         <v>Dirty Horchata</v>
       </c>
       <c r="D133" t="str">
-        <v>Iced Large (16oz) l Oat</v>
+        <v>Iced Large (16oz) l Almond</v>
       </c>
       <c r="E133">
         <v>180</v>
@@ -7990,13 +7990,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C134" t="str">
-        <v>Hojicha Oat Latte</v>
+        <v>Dirty Horchata</v>
       </c>
       <c r="D134" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz) l Oat</v>
       </c>
       <c r="E134">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="135">
@@ -8010,7 +8010,7 @@
         <v>Hojicha Oat Latte</v>
       </c>
       <c r="D135" t="str">
-        <v>Iced Regular (12oz) l Almond</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E135">
         <v>190</v>
@@ -8027,7 +8027,7 @@
         <v>Hojicha Oat Latte</v>
       </c>
       <c r="D136" t="str">
-        <v>Iced Regular (12oz) l Dairy</v>
+        <v>Iced Regular (12oz) l Almond</v>
       </c>
       <c r="E136">
         <v>190</v>
@@ -8044,10 +8044,10 @@
         <v>Hojicha Oat Latte</v>
       </c>
       <c r="D137" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz) l Dairy</v>
       </c>
       <c r="E137">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="138">
@@ -8061,7 +8061,7 @@
         <v>Hojicha Oat Latte</v>
       </c>
       <c r="D138" t="str">
-        <v>Iced Large (16oz) l Almond</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E138">
         <v>200</v>
@@ -8078,7 +8078,7 @@
         <v>Hojicha Oat Latte</v>
       </c>
       <c r="D139" t="str">
-        <v>Iced Large (16oz) l Dairy</v>
+        <v>Iced Large (16oz) l Almond</v>
       </c>
       <c r="E139">
         <v>200</v>
@@ -8092,13 +8092,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C140" t="str">
-        <v>Horchata</v>
+        <v>Hojicha Oat Latte</v>
       </c>
       <c r="D140" t="str">
-        <v>Iced Regular (12oz) l Dairy</v>
+        <v>Iced Large (16oz) l Dairy</v>
       </c>
       <c r="E140">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="141">
@@ -8112,7 +8112,7 @@
         <v>Horchata</v>
       </c>
       <c r="D141" t="str">
-        <v>Iced Regular (12oz) l Almond</v>
+        <v>Iced Regular (12oz) l Dairy</v>
       </c>
       <c r="E141">
         <v>150</v>
@@ -8129,7 +8129,7 @@
         <v>Horchata</v>
       </c>
       <c r="D142" t="str">
-        <v>Iced Regular (12oz) l Oat</v>
+        <v>Iced Regular (12oz) l Almond</v>
       </c>
       <c r="E142">
         <v>150</v>
@@ -8146,10 +8146,10 @@
         <v>Horchata</v>
       </c>
       <c r="D143" t="str">
-        <v>Iced Large (16oz) l Dairy</v>
+        <v>Iced Regular (12oz) l Oat</v>
       </c>
       <c r="E143">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="144">
@@ -8163,7 +8163,7 @@
         <v>Horchata</v>
       </c>
       <c r="D144" t="str">
-        <v>Iced Large (16oz) l Almond</v>
+        <v>Iced Large (16oz) l Dairy</v>
       </c>
       <c r="E144">
         <v>160</v>
@@ -8180,7 +8180,7 @@
         <v>Horchata</v>
       </c>
       <c r="D145" t="str">
-        <v>Iced Large (16oz) l Oat</v>
+        <v>Iced Large (16oz) l Almond</v>
       </c>
       <c r="E145">
         <v>160</v>
@@ -8194,10 +8194,10 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C146" t="str">
-        <v>Malted Chocolate Americano</v>
+        <v>Horchata</v>
       </c>
       <c r="D146" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz) l Oat</v>
       </c>
       <c r="E146">
         <v>160</v>
@@ -8214,10 +8214,10 @@
         <v>Malted Chocolate Americano</v>
       </c>
       <c r="D147" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E147">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="148">
@@ -8228,13 +8228,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C148" t="str">
-        <v>Malted Milk Protein Latte</v>
+        <v>Malted Chocolate Americano</v>
       </c>
       <c r="D148" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E148">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="149">
@@ -8248,10 +8248,10 @@
         <v>Malted Milk Protein Latte</v>
       </c>
       <c r="D149" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E149">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="150">
@@ -8262,13 +8262,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C150" t="str">
-        <v>Peanut Butter Protein Latte</v>
+        <v>Malted Milk Protein Latte</v>
       </c>
       <c r="D150" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E150">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="151">
@@ -8282,10 +8282,10 @@
         <v>Peanut Butter Protein Latte</v>
       </c>
       <c r="D151" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E151">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="152">
@@ -8296,13 +8296,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C152" t="str">
-        <v>Salted Caramel Matcha</v>
+        <v>Peanut Butter Protein Latte</v>
       </c>
       <c r="D152" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E152">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="153">
@@ -8316,10 +8316,10 @@
         <v>Salted Caramel Matcha</v>
       </c>
       <c r="D153" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E153">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="154">
@@ -8330,13 +8330,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C154" t="str">
-        <v>Salted Cream Matcha</v>
+        <v>Salted Caramel Matcha</v>
       </c>
       <c r="D154" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E154">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="155">
@@ -8350,10 +8350,10 @@
         <v>Salted Cream Matcha</v>
       </c>
       <c r="D155" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E155">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="156">
@@ -8364,13 +8364,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C156" t="str">
-        <v>Salted Dark Choc Protein Latte</v>
+        <v>Salted Cream Matcha</v>
       </c>
       <c r="D156" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E156">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="157">
@@ -8384,10 +8384,10 @@
         <v>Salted Dark Choc Protein Latte</v>
       </c>
       <c r="D157" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E157">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="158">
@@ -8398,13 +8398,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C158" t="str">
-        <v>Salted Dark Chocolate</v>
+        <v>Salted Dark Choc Protein Latte</v>
       </c>
       <c r="D158" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E158">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="159">
@@ -8415,13 +8415,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C159" t="str">
-        <v>Salted Honey Oat Latte</v>
+        <v>Salted Dark Chocolate</v>
       </c>
       <c r="D159" t="str">
-        <v>Iced Regular (12oz) l Dairy</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E159">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="160">
@@ -8435,7 +8435,7 @@
         <v>Salted Honey Oat Latte</v>
       </c>
       <c r="D160" t="str">
-        <v>Iced Regular (12oz) l Almond</v>
+        <v>Iced Regular (12oz) l Dairy</v>
       </c>
       <c r="E160">
         <v>200</v>
@@ -8452,7 +8452,7 @@
         <v>Salted Honey Oat Latte</v>
       </c>
       <c r="D161" t="str">
-        <v>Iced Regular (12oz) l Oat</v>
+        <v>Iced Regular (12oz) l Almond</v>
       </c>
       <c r="E161">
         <v>200</v>
@@ -8469,10 +8469,10 @@
         <v>Salted Honey Oat Latte</v>
       </c>
       <c r="D162" t="str">
-        <v>Iced Large (16oz) l Dairy</v>
+        <v>Iced Regular (12oz) l Oat</v>
       </c>
       <c r="E162">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="163">
@@ -8486,7 +8486,7 @@
         <v>Salted Honey Oat Latte</v>
       </c>
       <c r="D163" t="str">
-        <v>Iced Large (16oz) l Almond</v>
+        <v>Iced Large (16oz) l Dairy</v>
       </c>
       <c r="E163">
         <v>210</v>
@@ -8503,7 +8503,7 @@
         <v>Salted Honey Oat Latte</v>
       </c>
       <c r="D164" t="str">
-        <v>Iced Large (16oz) l Oat</v>
+        <v>Iced Large (16oz) l Almond</v>
       </c>
       <c r="E164">
         <v>210</v>
@@ -8517,13 +8517,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C165" t="str">
-        <v>Shaken Coconut Cold Brew</v>
+        <v>Salted Honey Oat Latte</v>
       </c>
       <c r="D165" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Large (16oz) l Oat</v>
       </c>
       <c r="E165">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="166">
@@ -8534,13 +8534,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C166" t="str">
-        <v>Shaken Creamy Lemonade</v>
+        <v>Shaken Coconut Cold Brew</v>
       </c>
       <c r="D166" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E166">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="167">
@@ -8551,13 +8551,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C167" t="str">
-        <v>Strawberry Cream Matcha</v>
+        <v>Shaken Creamy Lemonade</v>
       </c>
       <c r="D167" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E167">
-        <v>190</v>
+        <v>150</v>
       </c>
     </row>
     <row r="168">
@@ -8571,10 +8571,10 @@
         <v>Strawberry Cream Matcha</v>
       </c>
       <c r="D168" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E168">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="169">
@@ -8585,13 +8585,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C169" t="str">
-        <v>Strawberry Hojicha Latte</v>
+        <v>Strawberry Cream Matcha</v>
       </c>
       <c r="D169" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E169">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="170">
@@ -8605,10 +8605,10 @@
         <v>Strawberry Hojicha Latte</v>
       </c>
       <c r="D170" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E170">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="171">
@@ -8619,13 +8619,13 @@
         <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C171" t="str">
-        <v>Strawberry Milk</v>
+        <v>Strawberry Hojicha Latte</v>
       </c>
       <c r="D171" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E171">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="172">
@@ -8639,27 +8639,27 @@
         <v>Strawberry Milk</v>
       </c>
       <c r="D172" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E172">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>SNACKS</v>
+        <v>ICED</v>
       </c>
       <c r="B173" t="str">
-        <v>04 DOT SNACKS</v>
+        <v>03 DOT SIGNATURES</v>
       </c>
       <c r="C173" t="str">
-        <v>Black &amp; White Bar</v>
+        <v>Strawberry Milk</v>
       </c>
       <c r="D173" t="str">
-        <v/>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E173">
-        <v>90</v>
+        <v>160</v>
       </c>
     </row>
     <row r="174">
@@ -8670,13 +8670,13 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C174" t="str">
-        <v>Blitz Bar</v>
+        <v>Black &amp; White Bar</v>
       </c>
       <c r="D174" t="str">
-        <v>Dark Chocolate Dream</v>
+        <v/>
       </c>
       <c r="E174">
-        <v>130</v>
+        <v>90</v>
       </c>
     </row>
     <row r="175">
@@ -8690,7 +8690,7 @@
         <v>Blitz Bar</v>
       </c>
       <c r="D175" t="str">
-        <v>Classic Vanilla</v>
+        <v>Dark Chocolate Dream</v>
       </c>
       <c r="E175">
         <v>130</v>
@@ -8707,7 +8707,7 @@
         <v>Blitz Bar</v>
       </c>
       <c r="D176" t="str">
-        <v>Matcha Latte</v>
+        <v>Classic Vanilla</v>
       </c>
       <c r="E176">
         <v>130</v>
@@ -8721,13 +8721,13 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C177" t="str">
-        <v>Calamansi Protein Bar</v>
+        <v>Blitz Bar</v>
       </c>
       <c r="D177" t="str">
-        <v/>
+        <v>Matcha Latte</v>
       </c>
       <c r="E177">
-        <v>90</v>
+        <v>130</v>
       </c>
     </row>
     <row r="178">
@@ -8738,13 +8738,13 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C178" t="str">
-        <v>Chocolate Salt Bread</v>
+        <v>Calamansi Protein Bar</v>
       </c>
       <c r="D178" t="str">
         <v/>
       </c>
       <c r="E178">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="179">
@@ -8755,13 +8755,13 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C179" t="str">
-        <v>Corned Beef Pandesal</v>
+        <v>Chocolate Salt Bread</v>
       </c>
       <c r="D179" t="str">
         <v/>
       </c>
       <c r="E179">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="180">
@@ -8772,13 +8772,13 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C180" t="str">
-        <v>Double Chocolate Chip Cookie</v>
+        <v>Corned Beef Pandesal</v>
       </c>
       <c r="D180" t="str">
         <v/>
       </c>
       <c r="E180">
-        <v>120</v>
+        <v>55</v>
       </c>
     </row>
     <row r="181">
@@ -8789,13 +8789,13 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C181" t="str">
-        <v>Everything Dagel</v>
+        <v>Double Chocolate Chip Cookie</v>
       </c>
       <c r="D181" t="str">
         <v/>
       </c>
       <c r="E181">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="182">
@@ -8806,13 +8806,13 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C182" t="str">
-        <v>Ham Egg and Cheese Dagel</v>
+        <v>Everything Dagel</v>
       </c>
       <c r="D182" t="str">
         <v/>
       </c>
       <c r="E182">
-        <v>175</v>
+        <v>150</v>
       </c>
     </row>
     <row r="183">
@@ -8823,13 +8823,13 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C183" t="str">
-        <v>Oatmeal Crunch Protein Bar</v>
+        <v>Ham Egg and Cheese Dagel</v>
       </c>
       <c r="D183" t="str">
         <v/>
       </c>
       <c r="E183">
-        <v>90</v>
+        <v>175</v>
       </c>
     </row>
     <row r="184">
@@ -8840,13 +8840,13 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C184" t="str">
-        <v>Oatmeal Protein Cookie</v>
+        <v>Oatmeal Crunch Protein Bar</v>
       </c>
       <c r="D184" t="str">
         <v/>
       </c>
       <c r="E184">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="185">
@@ -8857,13 +8857,13 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C185" t="str">
-        <v>Peanut Butter Monkey Bar</v>
+        <v>Oatmeal Protein Cookie</v>
       </c>
       <c r="D185" t="str">
         <v/>
       </c>
       <c r="E185">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="186">
@@ -8874,13 +8874,13 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C186" t="str">
-        <v>Salt Bread</v>
+        <v>Peanut Butter Monkey Bar</v>
       </c>
       <c r="D186" t="str">
         <v/>
       </c>
       <c r="E186">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="187">
@@ -8891,13 +8891,13 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C187" t="str">
-        <v>Spinach Mushroom Pandesal</v>
+        <v>Salt Bread</v>
       </c>
       <c r="D187" t="str">
         <v/>
       </c>
       <c r="E187">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="188">
@@ -8908,47 +8908,47 @@
         <v>04 DOT SNACKS</v>
       </c>
       <c r="C188" t="str">
-        <v>Truffle Salt Bread</v>
+        <v>Spinach Mushroom Pandesal</v>
       </c>
       <c r="D188" t="str">
         <v/>
       </c>
       <c r="E188">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>MERCH</v>
+        <v>SNACKS</v>
       </c>
       <c r="B189" t="str">
-        <v>05 MERCH</v>
+        <v>04 DOT SNACKS</v>
       </c>
       <c r="C189" t="str">
-        <v>DC Tote Bag</v>
+        <v>Truffle Salt Bread</v>
       </c>
       <c r="D189" t="str">
         <v/>
       </c>
       <c r="E189">
-        <v>850</v>
+        <v>90</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>PROMO</v>
+        <v>MERCH</v>
       </c>
       <c r="B190" t="str">
         <v>05 MERCH</v>
       </c>
       <c r="C190" t="str">
-        <v>GC 100</v>
+        <v>DC Tote Bag</v>
       </c>
       <c r="D190" t="str">
         <v/>
       </c>
       <c r="E190">
-        <v>100</v>
+        <v>850</v>
       </c>
     </row>
     <row r="191">
@@ -8959,13 +8959,13 @@
         <v>05 MERCH</v>
       </c>
       <c r="C191" t="str">
-        <v>GC 300</v>
+        <v>GC 100</v>
       </c>
       <c r="D191" t="str">
         <v/>
       </c>
       <c r="E191">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="192">
@@ -8976,30 +8976,30 @@
         <v>05 MERCH</v>
       </c>
       <c r="C192" t="str">
-        <v>GC 500</v>
+        <v>GC 300</v>
       </c>
       <c r="D192" t="str">
         <v/>
       </c>
       <c r="E192">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>MERCH</v>
+        <v>PROMO</v>
       </c>
       <c r="B193" t="str">
         <v>05 MERCH</v>
       </c>
       <c r="C193" t="str">
-        <v>Gift Card Sleeves</v>
+        <v>GC 500</v>
       </c>
       <c r="D193" t="str">
         <v/>
       </c>
       <c r="E193">
-        <v>15</v>
+        <v>500</v>
       </c>
     </row>
     <row r="194">
@@ -9010,13 +9010,13 @@
         <v>05 MERCH</v>
       </c>
       <c r="C194" t="str">
-        <v>FREE Gift Card Sleeves</v>
+        <v>Gift Card Sleeves</v>
       </c>
       <c r="D194" t="str">
-        <v>total of 1000 php</v>
+        <v/>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="195">
@@ -9027,13 +9027,13 @@
         <v>05 MERCH</v>
       </c>
       <c r="C195" t="str">
-        <v>Tumbler Add-On</v>
+        <v>FREE Gift Card Sleeves</v>
       </c>
       <c r="D195" t="str">
-        <v>Set 1 (Straw + Rubber Stopper for Lid)</v>
+        <v>total of 1000 php</v>
       </c>
       <c r="E195">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -9047,10 +9047,10 @@
         <v>Tumbler Add-On</v>
       </c>
       <c r="D196" t="str">
-        <v>Set 2 (Silicone Boot + Handle)</v>
+        <v>Set 1 (Straw + Rubber Stopper for Lid)</v>
       </c>
       <c r="E196">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="197">
@@ -9061,13 +9061,13 @@
         <v>05 MERCH</v>
       </c>
       <c r="C197" t="str">
-        <v>Tumbler Holiday Set</v>
+        <v>Tumbler Add-On</v>
       </c>
       <c r="D197" t="str">
-        <v/>
+        <v>Set 2 (Silicone Boot + Handle)</v>
       </c>
       <c r="E197">
-        <v>600</v>
+        <v>180</v>
       </c>
     </row>
     <row r="198">
@@ -9078,30 +9078,30 @@
         <v>05 MERCH</v>
       </c>
       <c r="C198" t="str">
-        <v>Tumbler Only</v>
+        <v>Tumbler Holiday Set</v>
       </c>
       <c r="D198" t="str">
         <v/>
       </c>
       <c r="E198">
-        <v>450</v>
+        <v>600</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>PROMO</v>
+        <v>MERCH</v>
       </c>
       <c r="B199" t="str">
-        <v>06 PROMO</v>
+        <v>05 MERCH</v>
       </c>
       <c r="C199" t="str">
-        <v>Bring your Own Tumbler</v>
+        <v>Tumbler Only</v>
       </c>
       <c r="D199" t="str">
         <v/>
       </c>
       <c r="E199">
-        <v>-10</v>
+        <v>450</v>
       </c>
     </row>
     <row r="200">
@@ -9112,27 +9112,27 @@
         <v>06 PROMO</v>
       </c>
       <c r="C200" t="str">
-        <v>MBxCB Discount Deals</v>
+        <v>Bring your Own Tumbler</v>
       </c>
       <c r="D200" t="str">
         <v/>
       </c>
       <c r="E200">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>ICED</v>
+        <v>PROMO</v>
       </c>
       <c r="B201" t="str">
         <v>06 PROMO</v>
       </c>
       <c r="C201" t="str">
-        <v>GO Free Drink - Americano</v>
+        <v>MBxCB Discount Deals</v>
       </c>
       <c r="D201" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v/>
       </c>
       <c r="E201">
         <v>0</v>
@@ -9140,7 +9140,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>PROMO</v>
+        <v>ICED</v>
       </c>
       <c r="B202" t="str">
         <v>06 PROMO</v>
@@ -9149,7 +9149,7 @@
         <v>GO Free Drink - Americano</v>
       </c>
       <c r="D202" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -9157,16 +9157,16 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>ICED</v>
+        <v>PROMO</v>
       </c>
       <c r="B203" t="str">
         <v>06 PROMO</v>
       </c>
       <c r="C203" t="str">
-        <v>GO Free Drink - Latte</v>
+        <v>GO Free Drink - Americano</v>
       </c>
       <c r="D203" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -9174,7 +9174,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>PROMO</v>
+        <v>ICED</v>
       </c>
       <c r="B204" t="str">
         <v>06 PROMO</v>
@@ -9183,7 +9183,7 @@
         <v>GO Free Drink - Latte</v>
       </c>
       <c r="D204" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -9191,16 +9191,16 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>ICED</v>
+        <v>PROMO</v>
       </c>
       <c r="B205" t="str">
         <v>06 PROMO</v>
       </c>
       <c r="C205" t="str">
-        <v>GO Free Drink - Matcha</v>
+        <v>GO Free Drink - Latte</v>
       </c>
       <c r="D205" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -9208,7 +9208,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>PROMO</v>
+        <v>ICED</v>
       </c>
       <c r="B206" t="str">
         <v>06 PROMO</v>
@@ -9217,7 +9217,7 @@
         <v>GO Free Drink - Matcha</v>
       </c>
       <c r="D206" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -9225,16 +9225,16 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>ICED</v>
+        <v>PROMO</v>
       </c>
       <c r="B207" t="str">
         <v>06 PROMO</v>
       </c>
       <c r="C207" t="str">
-        <v>GO Free Drink - Spanish Latte</v>
+        <v>GO Free Drink - Matcha</v>
       </c>
       <c r="D207" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -9242,7 +9242,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>PROMO</v>
+        <v>ICED</v>
       </c>
       <c r="B208" t="str">
         <v>06 PROMO</v>
@@ -9251,7 +9251,7 @@
         <v>GO Free Drink - Spanish Latte</v>
       </c>
       <c r="D208" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -9259,16 +9259,16 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>LOYALTY CARD</v>
+        <v>PROMO</v>
       </c>
       <c r="B209" t="str">
-        <v>07 LOYALTY CARD</v>
+        <v>06 PROMO</v>
       </c>
       <c r="C209" t="str">
-        <v>LC Free Tumbler</v>
+        <v>GO Free Drink - Spanish Latte</v>
       </c>
       <c r="D209" t="str">
-        <v/>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -9282,13 +9282,13 @@
         <v>07 LOYALTY CARD</v>
       </c>
       <c r="C210" t="str">
-        <v>LC Free Upsize</v>
+        <v>LC Free Tumbler</v>
       </c>
       <c r="D210" t="str">
         <v/>
       </c>
       <c r="E210">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -9299,30 +9299,30 @@
         <v>07 LOYALTY CARD</v>
       </c>
       <c r="C211" t="str">
-        <v>LC Free 16oz</v>
+        <v>LC Free Upsize</v>
       </c>
       <c r="D211" t="str">
         <v/>
       </c>
       <c r="E211">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>ADD ONS</v>
+        <v>LOYALTY CARD</v>
       </c>
       <c r="B212" t="str">
-        <v>08 DEL - ADD ONS</v>
+        <v>07 LOYALTY CARD</v>
       </c>
       <c r="C212" t="str">
-        <v>ADD ONS MISC</v>
+        <v>LC Free 16oz</v>
       </c>
       <c r="D212" t="str">
-        <v>Cereal Crunch</v>
+        <v/>
       </c>
       <c r="E212">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -9336,10 +9336,10 @@
         <v>ADD ONS MISC</v>
       </c>
       <c r="D213" t="str">
-        <v>Coconut Water</v>
+        <v>Cereal Crunch</v>
       </c>
       <c r="E213">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="214">
@@ -9353,10 +9353,10 @@
         <v>ADD ONS MISC</v>
       </c>
       <c r="D214" t="str">
-        <v>Decaf Espresso Shot</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E214">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="215">
@@ -9370,7 +9370,7 @@
         <v>ADD ONS MISC</v>
       </c>
       <c r="D215" t="str">
-        <v>Espresso Shot</v>
+        <v>Decaf Espresso Shot</v>
       </c>
       <c r="E215">
         <v>55</v>
@@ -9387,7 +9387,7 @@
         <v>ADD ONS MISC</v>
       </c>
       <c r="D216" t="str">
-        <v>Hojicha Powder</v>
+        <v>Espresso Shot</v>
       </c>
       <c r="E216">
         <v>55</v>
@@ -9404,10 +9404,10 @@
         <v>ADD ONS MISC</v>
       </c>
       <c r="D217" t="str">
-        <v>Krea Creatine Wheyl</v>
+        <v>Hojicha Powder</v>
       </c>
       <c r="E217">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="218">
@@ -9421,7 +9421,7 @@
         <v>ADD ONS MISC</v>
       </c>
       <c r="D218" t="str">
-        <v>Matcha Powder</v>
+        <v>Krea Creatine Wheyl</v>
       </c>
       <c r="E218">
         <v>50</v>
@@ -9438,10 +9438,10 @@
         <v>ADD ONS MISC</v>
       </c>
       <c r="D219" t="str">
-        <v>Water Bottle</v>
+        <v>Matcha Powder</v>
       </c>
       <c r="E219">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="220">
@@ -9455,10 +9455,10 @@
         <v>ADD ONS MISC</v>
       </c>
       <c r="D220" t="str">
-        <v>Whey Protein</v>
+        <v>Water Bottle</v>
       </c>
       <c r="E220">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="221">
@@ -9469,10 +9469,10 @@
         <v>08 DEL - ADD ONS</v>
       </c>
       <c r="C221" t="str">
-        <v>ADD ONS MILK</v>
+        <v>ADD ONS MISC</v>
       </c>
       <c r="D221" t="str">
-        <v>Almond Milk</v>
+        <v>Whey Protein</v>
       </c>
       <c r="E221">
         <v>60</v>
@@ -9489,10 +9489,10 @@
         <v>ADD ONS MILK</v>
       </c>
       <c r="D222" t="str">
-        <v>Dehusk Coconut Milk</v>
+        <v>Almond Milk</v>
       </c>
       <c r="E222">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="223">
@@ -9506,10 +9506,10 @@
         <v>ADD ONS MILK</v>
       </c>
       <c r="D223" t="str">
-        <v>Oat Milk</v>
+        <v>Dehusk Coconut Milk</v>
       </c>
       <c r="E223">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="224">
@@ -9520,13 +9520,13 @@
         <v>08 DEL - ADD ONS</v>
       </c>
       <c r="C224" t="str">
-        <v>ADD ONS SYRUPS</v>
+        <v>ADD ONS MILK</v>
       </c>
       <c r="D224" t="str">
-        <v>Brown Sugar Syrup</v>
+        <v>Oat Milk</v>
       </c>
       <c r="E224">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="225">
@@ -9537,10 +9537,10 @@
         <v>08 DEL - ADD ONS</v>
       </c>
       <c r="C225" t="str">
-        <v>ADD ONS SYRUPS</v>
+        <v>ADD ONS MILK</v>
       </c>
       <c r="D225" t="str">
-        <v>Burnt Vanilla Syrup</v>
+        <v>Dairy Milk</v>
       </c>
       <c r="E225">
         <v>45</v>
@@ -9557,7 +9557,7 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D226" t="str">
-        <v>Butterscotch Syrup</v>
+        <v>Brown Sugar Syrup</v>
       </c>
       <c r="E226">
         <v>45</v>
@@ -9574,10 +9574,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D227" t="str">
-        <v>Caramelized Banana Syrup</v>
+        <v>Burnt Vanilla Syrup</v>
       </c>
       <c r="E227">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="228">
@@ -9591,7 +9591,7 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D228" t="str">
-        <v>French Vanilla Syrup</v>
+        <v>Butterscotch Syrup</v>
       </c>
       <c r="E228">
         <v>45</v>
@@ -9608,10 +9608,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D229" t="str">
-        <v>Honey Syrup</v>
+        <v>Caramelized Banana Syrup</v>
       </c>
       <c r="E229">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="230">
@@ -9625,7 +9625,7 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D230" t="str">
-        <v>Peanut Butter Syrup</v>
+        <v>French Vanilla Syrup</v>
       </c>
       <c r="E230">
         <v>45</v>
@@ -9642,10 +9642,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D231" t="str">
-        <v>Salted Caramel Syrup</v>
+        <v>Honey Syrup</v>
       </c>
       <c r="E231">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="232">
@@ -9659,7 +9659,7 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D232" t="str">
-        <v>Signature Mocha Syrup</v>
+        <v>Peanut Butter Syrup</v>
       </c>
       <c r="E232">
         <v>45</v>
@@ -9676,10 +9676,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D233" t="str">
-        <v>Sugar Syrup</v>
+        <v>Salted Caramel Syrup</v>
       </c>
       <c r="E233">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="234">
@@ -9693,7 +9693,7 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D234" t="str">
-        <v>Spanish Latte Syrup</v>
+        <v>Signature Mocha Syrup</v>
       </c>
       <c r="E234">
         <v>45</v>
@@ -9710,10 +9710,10 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D235" t="str">
-        <v>Strawberry Puree</v>
+        <v>Sugar Syrup</v>
       </c>
       <c r="E235">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -9727,7 +9727,7 @@
         <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D236" t="str">
-        <v>White Chocolate Mocha Syrup</v>
+        <v>Spanish Latte Syrup</v>
       </c>
       <c r="E236">
         <v>45</v>
@@ -9741,10 +9741,10 @@
         <v>08 DEL - ADD ONS</v>
       </c>
       <c r="C237" t="str">
-        <v>ADD ONS FOAM</v>
+        <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D237" t="str">
-        <v>Chocolate Foam</v>
+        <v>Strawberry Puree</v>
       </c>
       <c r="E237">
         <v>55</v>
@@ -9758,13 +9758,13 @@
         <v>08 DEL - ADD ONS</v>
       </c>
       <c r="C238" t="str">
-        <v>ADD ONS FOAM</v>
+        <v>ADD ONS SYRUPS</v>
       </c>
       <c r="D238" t="str">
-        <v>Black Sesame Cold Foam</v>
+        <v>White Chocolate Mocha Syrup</v>
       </c>
       <c r="E238">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="239">
@@ -9778,10 +9778,10 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D239" t="str">
-        <v>Hojicha Cold Foam</v>
+        <v>Chocolate Foam</v>
       </c>
       <c r="E239">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="240">
@@ -9795,7 +9795,7 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D240" t="str">
-        <v>Malted Chocolate Foam</v>
+        <v>Black Sesame Cold Foam</v>
       </c>
       <c r="E240">
         <v>65</v>
@@ -9812,7 +9812,7 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D241" t="str">
-        <v>Matcha Cream Foam</v>
+        <v>Hojicha Cold Foam</v>
       </c>
       <c r="E241">
         <v>65</v>
@@ -9829,7 +9829,7 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D242" t="str">
-        <v>Rock Salt Cheese Foam</v>
+        <v>Malted Chocolate Foam</v>
       </c>
       <c r="E242">
         <v>65</v>
@@ -9846,10 +9846,10 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D243" t="str">
-        <v>Salted Caramel Foam</v>
+        <v>Matcha Cream Foam</v>
       </c>
       <c r="E243">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="244">
@@ -9863,7 +9863,7 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D244" t="str">
-        <v>Salted Cream Foam</v>
+        <v>Rock Salt Cheese Foam</v>
       </c>
       <c r="E244">
         <v>65</v>
@@ -9880,49 +9880,49 @@
         <v>ADD ONS FOAM</v>
       </c>
       <c r="D245" t="str">
-        <v>Strawberry Cream Foam</v>
+        <v>Salted Caramel Foam</v>
       </c>
       <c r="E245">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>ICED</v>
+        <v>ADD ONS</v>
       </c>
       <c r="B246" t="str">
-        <v>09 DEL - CLASSICS</v>
+        <v>08 DEL - ADD ONS</v>
       </c>
       <c r="C246" t="str">
-        <v>Americano</v>
+        <v>ADD ONS FOAM</v>
       </c>
       <c r="D246" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Salted Cream Foam</v>
       </c>
       <c r="E246">
-        <v>150</v>
+        <v>65</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>ICED</v>
+        <v>ADD ONS</v>
       </c>
       <c r="B247" t="str">
-        <v>09 DEL - CLASSICS</v>
+        <v>08 DEL - ADD ONS</v>
       </c>
       <c r="C247" t="str">
-        <v>Americano</v>
+        <v>ADD ONS FOAM</v>
       </c>
       <c r="D247" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Strawberry Cream Foam</v>
       </c>
       <c r="E247">
-        <v>160</v>
+        <v>65</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B248" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -9931,7 +9931,7 @@
         <v>Americano</v>
       </c>
       <c r="D248" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E248">
         <v>150</v>
@@ -9939,7 +9939,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B249" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -9948,7 +9948,7 @@
         <v>Americano</v>
       </c>
       <c r="D249" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E249">
         <v>160</v>
@@ -9956,41 +9956,41 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B250" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C250" t="str">
-        <v>Burnt Vanilla</v>
+        <v>Americano</v>
       </c>
       <c r="D250" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E250">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B251" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C251" t="str">
-        <v>Burnt Vanilla</v>
+        <v>Americano</v>
       </c>
       <c r="D251" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E251">
-        <v>210</v>
+        <v>160</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B252" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -9999,7 +9999,7 @@
         <v>Burnt Vanilla</v>
       </c>
       <c r="D252" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E252">
         <v>200</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B253" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10016,7 +10016,7 @@
         <v>Burnt Vanilla</v>
       </c>
       <c r="D253" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E253">
         <v>210</v>
@@ -10024,41 +10024,41 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B254" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C254" t="str">
-        <v>Butterscotch</v>
+        <v>Burnt Vanilla</v>
       </c>
       <c r="D254" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E254">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B255" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C255" t="str">
-        <v>Butterscotch</v>
+        <v>Burnt Vanilla</v>
       </c>
       <c r="D255" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E255">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B256" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10067,7 +10067,7 @@
         <v>Butterscotch</v>
       </c>
       <c r="D256" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E256">
         <v>190</v>
@@ -10075,7 +10075,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B257" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10084,7 +10084,7 @@
         <v>Butterscotch</v>
       </c>
       <c r="D257" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E257">
         <v>200</v>
@@ -10092,36 +10092,36 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B258" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C258" t="str">
-        <v>Cold Brew</v>
+        <v>Butterscotch</v>
       </c>
       <c r="D258" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E258">
-        <v>160</v>
+        <v>190</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B259" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C259" t="str">
-        <v>Cold Brew</v>
+        <v>Butterscotch</v>
       </c>
       <c r="D259" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E259">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="260">
@@ -10132,13 +10132,13 @@
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C260" t="str">
-        <v>Dirty Matcha</v>
+        <v>Cold Brew</v>
       </c>
       <c r="D260" t="str">
         <v>Iced Regular (12oz)</v>
       </c>
       <c r="E260">
-        <v>220</v>
+        <v>160</v>
       </c>
     </row>
     <row r="261">
@@ -10149,18 +10149,18 @@
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C261" t="str">
-        <v>Dirty Matcha</v>
+        <v>Cold Brew</v>
       </c>
       <c r="D261" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E261">
-        <v>230</v>
+        <v>170</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B262" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10169,7 +10169,7 @@
         <v>Dirty Matcha</v>
       </c>
       <c r="D262" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E262">
         <v>220</v>
@@ -10177,7 +10177,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B263" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10186,7 +10186,7 @@
         <v>Dirty Matcha</v>
       </c>
       <c r="D263" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E263">
         <v>230</v>
@@ -10194,41 +10194,41 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B264" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C264" t="str">
-        <v>Latte</v>
+        <v>Dirty Matcha</v>
       </c>
       <c r="D264" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E264">
-        <v>170</v>
+        <v>220</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B265" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C265" t="str">
-        <v>Latte</v>
+        <v>Dirty Matcha</v>
       </c>
       <c r="D265" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E265">
-        <v>180</v>
+        <v>230</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B266" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10237,7 +10237,7 @@
         <v>Latte</v>
       </c>
       <c r="D266" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E266">
         <v>170</v>
@@ -10245,7 +10245,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B267" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10254,7 +10254,7 @@
         <v>Latte</v>
       </c>
       <c r="D267" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E267">
         <v>180</v>
@@ -10262,41 +10262,41 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B268" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C268" t="str">
-        <v>Matcha</v>
+        <v>Latte</v>
       </c>
       <c r="D268" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E268">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B269" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C269" t="str">
-        <v>Matcha</v>
+        <v>Latte</v>
       </c>
       <c r="D269" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E269">
-        <v>210</v>
+        <v>180</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B270" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10305,7 +10305,7 @@
         <v>Matcha</v>
       </c>
       <c r="D270" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E270">
         <v>200</v>
@@ -10313,7 +10313,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B271" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10322,7 +10322,7 @@
         <v>Matcha</v>
       </c>
       <c r="D271" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E271">
         <v>210</v>
@@ -10330,41 +10330,41 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B272" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C272" t="str">
-        <v>Salted Caramel</v>
+        <v>Matcha</v>
       </c>
       <c r="D272" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E272">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B273" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C273" t="str">
-        <v>Salted Caramel</v>
+        <v>Matcha</v>
       </c>
       <c r="D273" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E273">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B274" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10373,7 +10373,7 @@
         <v>Salted Caramel</v>
       </c>
       <c r="D274" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E274">
         <v>190</v>
@@ -10381,7 +10381,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B275" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10390,7 +10390,7 @@
         <v>Salted Caramel</v>
       </c>
       <c r="D275" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E275">
         <v>200</v>
@@ -10398,16 +10398,16 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B276" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C276" t="str">
-        <v>Signature Mocha</v>
+        <v>Salted Caramel</v>
       </c>
       <c r="D276" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E276">
         <v>190</v>
@@ -10415,16 +10415,16 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B277" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C277" t="str">
-        <v>Signature Mocha</v>
+        <v>Salted Caramel</v>
       </c>
       <c r="D277" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E277">
         <v>200</v>
@@ -10432,7 +10432,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B278" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10441,7 +10441,7 @@
         <v>Signature Mocha</v>
       </c>
       <c r="D278" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E278">
         <v>190</v>
@@ -10449,7 +10449,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B279" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10458,7 +10458,7 @@
         <v>Signature Mocha</v>
       </c>
       <c r="D279" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E279">
         <v>200</v>
@@ -10466,16 +10466,16 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B280" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C280" t="str">
-        <v>Spanish Latte</v>
+        <v>Signature Mocha</v>
       </c>
       <c r="D280" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E280">
         <v>190</v>
@@ -10483,16 +10483,16 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B281" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C281" t="str">
-        <v>Spanish Latte</v>
+        <v>Signature Mocha</v>
       </c>
       <c r="D281" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E281">
         <v>200</v>
@@ -10500,7 +10500,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B282" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10509,7 +10509,7 @@
         <v>Spanish Latte</v>
       </c>
       <c r="D282" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E282">
         <v>190</v>
@@ -10517,7 +10517,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B283" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10526,7 +10526,7 @@
         <v>Spanish Latte</v>
       </c>
       <c r="D283" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E283">
         <v>200</v>
@@ -10534,16 +10534,16 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B284" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C284" t="str">
-        <v>White Chocolate Mocha</v>
+        <v>Spanish Latte</v>
       </c>
       <c r="D284" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E284">
         <v>190</v>
@@ -10551,16 +10551,16 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B285" t="str">
         <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C285" t="str">
-        <v>White Chocolate Mocha</v>
+        <v>Spanish Latte</v>
       </c>
       <c r="D285" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E285">
         <v>200</v>
@@ -10568,7 +10568,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B286" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10577,7 +10577,7 @@
         <v>White Chocolate Mocha</v>
       </c>
       <c r="D286" t="str">
-        <v>Hot Regular (12oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E286">
         <v>190</v>
@@ -10585,7 +10585,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B287" t="str">
         <v>09 DEL - CLASSICS</v>
@@ -10594,7 +10594,7 @@
         <v>White Chocolate Mocha</v>
       </c>
       <c r="D287" t="str">
-        <v>Hot Large (16oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E287">
         <v>200</v>
@@ -10602,36 +10602,36 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B288" t="str">
-        <v>10 DEL - SIGNATURES</v>
+        <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C288" t="str">
-        <v>Black Sesame Hojicha Latte</v>
+        <v>White Chocolate Mocha</v>
       </c>
       <c r="D288" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular (12oz)</v>
       </c>
       <c r="E288">
-        <v>260</v>
+        <v>190</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B289" t="str">
-        <v>10 DEL - SIGNATURES</v>
+        <v>09 DEL - CLASSICS</v>
       </c>
       <c r="C289" t="str">
-        <v>Black Sesame Hojicha Latte</v>
+        <v>White Chocolate Mocha</v>
       </c>
       <c r="D289" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Hot Large (16oz)</v>
       </c>
       <c r="E289">
-        <v>270</v>
+        <v>200</v>
       </c>
     </row>
     <row r="290">
@@ -10642,13 +10642,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C290" t="str">
-        <v>Caramelized Banana Hojicha Latte</v>
+        <v>Black Sesame Hojicha Latte</v>
       </c>
       <c r="D290" t="str">
         <v>Iced Regular (12oz)</v>
       </c>
       <c r="E290">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row r="291">
@@ -10659,13 +10659,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C291" t="str">
-        <v>Caramelized Banana Hojicha Latte</v>
+        <v>Black Sesame Hojicha Latte</v>
       </c>
       <c r="D291" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E291">
-        <v>240</v>
+        <v>270</v>
       </c>
     </row>
     <row r="292">
@@ -10676,13 +10676,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C292" t="str">
-        <v>Cereal Milk</v>
+        <v>Caramelized Banana Hojicha Latte</v>
       </c>
       <c r="D292" t="str">
         <v>Iced Regular (12oz)</v>
       </c>
       <c r="E292">
-        <v>190</v>
+        <v>230</v>
       </c>
     </row>
     <row r="293">
@@ -10693,13 +10693,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C293" t="str">
-        <v>Cereal Milk</v>
+        <v>Caramelized Banana Hojicha Latte</v>
       </c>
       <c r="D293" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E293">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="294">
@@ -10710,13 +10710,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C294" t="str">
-        <v>Chocolate Milk</v>
+        <v>Cereal Milk</v>
       </c>
       <c r="D294" t="str">
         <v>Iced Regular (12oz)</v>
       </c>
       <c r="E294">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
     <row r="295">
@@ -10727,18 +10727,18 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C295" t="str">
-        <v>Chocolate Milk</v>
+        <v>Cereal Milk</v>
       </c>
       <c r="D295" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E295">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B296" t="str">
         <v>10 DEL - SIGNATURES</v>
@@ -10747,7 +10747,7 @@
         <v>Chocolate Milk</v>
       </c>
       <c r="D296" t="str">
-        <v>Hot Regular 12oz.</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E296">
         <v>170</v>
@@ -10755,7 +10755,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>HOT</v>
+        <v>ICED</v>
       </c>
       <c r="B297" t="str">
         <v>10 DEL - SIGNATURES</v>
@@ -10764,7 +10764,7 @@
         <v>Chocolate Milk</v>
       </c>
       <c r="D297" t="str">
-        <v>Hot Large 16oz.</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E297">
         <v>180</v>
@@ -10772,36 +10772,36 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B298" t="str">
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C298" t="str">
-        <v>Coco Americano</v>
+        <v>Chocolate Milk</v>
       </c>
       <c r="D298" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Hot Regular 12oz.</v>
       </c>
       <c r="E298">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>ICED</v>
+        <v>HOT</v>
       </c>
       <c r="B299" t="str">
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C299" t="str">
-        <v>Coco Americano</v>
+        <v>Chocolate Milk</v>
       </c>
       <c r="D299" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Hot Large 16oz.</v>
       </c>
       <c r="E299">
-        <v>210</v>
+        <v>180</v>
       </c>
     </row>
     <row r="300">
@@ -10812,13 +10812,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C300" t="str">
-        <v>CocoChata</v>
+        <v>Coco Americano</v>
       </c>
       <c r="D300" t="str">
         <v>Iced Regular (12oz)</v>
       </c>
       <c r="E300">
-        <v>225</v>
+        <v>200</v>
       </c>
     </row>
     <row r="301">
@@ -10829,13 +10829,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C301" t="str">
-        <v>CocoChata</v>
+        <v>Coco Americano</v>
       </c>
       <c r="D301" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E301">
-        <v>235</v>
+        <v>210</v>
       </c>
     </row>
     <row r="302">
@@ -10846,7 +10846,7 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C302" t="str">
-        <v>Coconut Cream Cold Brew</v>
+        <v>CocoChata</v>
       </c>
       <c r="D302" t="str">
         <v>Iced Regular (12oz)</v>
@@ -10863,7 +10863,7 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C303" t="str">
-        <v>Coconut Cream Cold Brew</v>
+        <v>CocoChata</v>
       </c>
       <c r="D303" t="str">
         <v>Iced Large (16oz)</v>
@@ -10880,13 +10880,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C304" t="str">
-        <v>Cookie Butter Oat Latte</v>
+        <v>Coconut Cream Cold Brew</v>
       </c>
       <c r="D304" t="str">
-        <v>Iced Regular (12oz) l Dairy</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E304">
-        <v>240</v>
+        <v>225</v>
       </c>
     </row>
     <row r="305">
@@ -10897,13 +10897,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C305" t="str">
-        <v>Cookie Butter Oat Latte</v>
+        <v>Coconut Cream Cold Brew</v>
       </c>
       <c r="D305" t="str">
-        <v>Iced Regular (12oz) l Almond</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E305">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="306">
@@ -10917,7 +10917,7 @@
         <v>Cookie Butter Oat Latte</v>
       </c>
       <c r="D306" t="str">
-        <v>Iced Regular (12oz) l Oat</v>
+        <v>Iced Regular (12oz) l Dairy</v>
       </c>
       <c r="E306">
         <v>240</v>
@@ -10934,10 +10934,10 @@
         <v>Cookie Butter Oat Latte</v>
       </c>
       <c r="D307" t="str">
-        <v>Iced Large (16oz) l Dairy</v>
+        <v>Iced Regular (12oz) l Almond</v>
       </c>
       <c r="E307">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="308">
@@ -10951,10 +10951,10 @@
         <v>Cookie Butter Oat Latte</v>
       </c>
       <c r="D308" t="str">
-        <v>Iced Large (16oz) l Almond</v>
+        <v>Iced Regular (12oz) l Oat</v>
       </c>
       <c r="E308">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="309">
@@ -10968,7 +10968,7 @@
         <v>Cookie Butter Oat Latte</v>
       </c>
       <c r="D309" t="str">
-        <v>Iced Large (16oz) l Oat</v>
+        <v>Iced Large (16oz) l Dairy</v>
       </c>
       <c r="E309">
         <v>250</v>
@@ -10982,13 +10982,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C310" t="str">
-        <v>Creamy Coco Hojicha</v>
+        <v>Cookie Butter Oat Latte</v>
       </c>
       <c r="D310" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz) l Almond</v>
       </c>
       <c r="E310">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row r="311">
@@ -10999,13 +10999,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C311" t="str">
-        <v>Creamy Coco Hojicha</v>
+        <v>Cookie Butter Oat Latte</v>
       </c>
       <c r="D311" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Large (16oz) l Oat</v>
       </c>
       <c r="E311">
-        <v>240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="312">
@@ -11016,7 +11016,7 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C312" t="str">
-        <v>Creamy Coco Matcha</v>
+        <v>Creamy Coco Hojicha</v>
       </c>
       <c r="D312" t="str">
         <v>Iced Regular (12oz)</v>
@@ -11033,7 +11033,7 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C313" t="str">
-        <v>Creamy Coco Matcha</v>
+        <v>Creamy Coco Hojicha</v>
       </c>
       <c r="D313" t="str">
         <v>Iced Large (16oz)</v>
@@ -11050,13 +11050,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C314" t="str">
-        <v>Dirty Cereal</v>
+        <v>Creamy Coco Matcha</v>
       </c>
       <c r="D314" t="str">
         <v>Iced Regular (12oz)</v>
       </c>
       <c r="E314">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="315">
@@ -11067,13 +11067,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C315" t="str">
-        <v>Dirty Cereal</v>
+        <v>Creamy Coco Matcha</v>
       </c>
       <c r="D315" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E315">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="316">
@@ -11084,13 +11084,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C316" t="str">
-        <v>Dirty Coco</v>
+        <v>Dirty Cereal</v>
       </c>
       <c r="D316" t="str">
         <v>Iced Regular (12oz)</v>
       </c>
       <c r="E316">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="317">
@@ -11101,13 +11101,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C317" t="str">
-        <v>Dirty Coco</v>
+        <v>Dirty Cereal</v>
       </c>
       <c r="D317" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E317">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="318">
@@ -11118,10 +11118,10 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C318" t="str">
-        <v>Dirty Horchata</v>
+        <v>Dirty Coco</v>
       </c>
       <c r="D318" t="str">
-        <v>Iced Regular (12oz) l Dairy</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E318">
         <v>210</v>
@@ -11135,13 +11135,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C319" t="str">
-        <v>Dirty Horchata</v>
+        <v>Dirty Coco</v>
       </c>
       <c r="D319" t="str">
-        <v>Iced Regular (12oz) l Almond</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E319">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="320">
@@ -11155,7 +11155,7 @@
         <v>Dirty Horchata</v>
       </c>
       <c r="D320" t="str">
-        <v>Iced Regular (12oz) l Oat</v>
+        <v>Iced Regular (12oz) l Dairy</v>
       </c>
       <c r="E320">
         <v>210</v>
@@ -11172,10 +11172,10 @@
         <v>Dirty Horchata</v>
       </c>
       <c r="D321" t="str">
-        <v>Iced Large (16oz) l Dairy</v>
+        <v>Iced Regular (12oz) l Almond</v>
       </c>
       <c r="E321">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="322">
@@ -11189,10 +11189,10 @@
         <v>Dirty Horchata</v>
       </c>
       <c r="D322" t="str">
-        <v>Iced Large (16oz) l Almond</v>
+        <v>Iced Regular (12oz) l Oat</v>
       </c>
       <c r="E322">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="323">
@@ -11206,7 +11206,7 @@
         <v>Dirty Horchata</v>
       </c>
       <c r="D323" t="str">
-        <v>Iced Large (16oz) l Oat</v>
+        <v>Iced Large (16oz) l Dairy</v>
       </c>
       <c r="E323">
         <v>220</v>
@@ -11220,13 +11220,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C324" t="str">
-        <v>Hojicha Oat Latte</v>
+        <v>Dirty Horchata</v>
       </c>
       <c r="D324" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz) l Almond</v>
       </c>
       <c r="E324">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="325">
@@ -11237,13 +11237,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C325" t="str">
-        <v>Hojicha Oat Latte</v>
+        <v>Dirty Horchata</v>
       </c>
       <c r="D325" t="str">
-        <v>Iced Regular (12oz) l Almond</v>
+        <v>Iced Large (16oz) l Oat</v>
       </c>
       <c r="E325">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="326">
@@ -11257,7 +11257,7 @@
         <v>Hojicha Oat Latte</v>
       </c>
       <c r="D326" t="str">
-        <v>Iced Regular (12oz) l Dairy</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E326">
         <v>230</v>
@@ -11274,10 +11274,10 @@
         <v>Hojicha Oat Latte</v>
       </c>
       <c r="D327" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz) l Almond</v>
       </c>
       <c r="E327">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="328">
@@ -11291,10 +11291,10 @@
         <v>Hojicha Oat Latte</v>
       </c>
       <c r="D328" t="str">
-        <v>Iced Large (16oz) l Almond</v>
+        <v>Iced Regular (12oz) l Dairy</v>
       </c>
       <c r="E328">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="329">
@@ -11308,7 +11308,7 @@
         <v>Hojicha Oat Latte</v>
       </c>
       <c r="D329" t="str">
-        <v>Iced Large (16oz) l Dairy</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E329">
         <v>240</v>
@@ -11322,13 +11322,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C330" t="str">
-        <v>Horchata</v>
+        <v>Hojicha Oat Latte</v>
       </c>
       <c r="D330" t="str">
-        <v>Iced Regular (12oz) l Dairy</v>
+        <v>Iced Large (16oz) l Almond</v>
       </c>
       <c r="E330">
-        <v>190</v>
+        <v>240</v>
       </c>
     </row>
     <row r="331">
@@ -11339,13 +11339,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C331" t="str">
-        <v>Horchata</v>
+        <v>Hojicha Oat Latte</v>
       </c>
       <c r="D331" t="str">
-        <v>Iced Regular (12oz) l Almond</v>
+        <v>Iced Large (16oz) l Dairy</v>
       </c>
       <c r="E331">
-        <v>190</v>
+        <v>240</v>
       </c>
     </row>
     <row r="332">
@@ -11359,7 +11359,7 @@
         <v>Horchata</v>
       </c>
       <c r="D332" t="str">
-        <v>Iced Regular (12oz) l Oat</v>
+        <v>Iced Regular (12oz) l Dairy</v>
       </c>
       <c r="E332">
         <v>190</v>
@@ -11376,10 +11376,10 @@
         <v>Horchata</v>
       </c>
       <c r="D333" t="str">
-        <v>Iced Large (16oz) l Dairy</v>
+        <v>Iced Regular (12oz) l Almond</v>
       </c>
       <c r="E333">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="334">
@@ -11393,10 +11393,10 @@
         <v>Horchata</v>
       </c>
       <c r="D334" t="str">
-        <v>Iced Large (16oz) l Almond</v>
+        <v>Iced Regular (12oz) l Oat</v>
       </c>
       <c r="E334">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="335">
@@ -11410,7 +11410,7 @@
         <v>Horchata</v>
       </c>
       <c r="D335" t="str">
-        <v>Iced Large (16oz) l Oat</v>
+        <v>Iced Large (16oz) l Dairy</v>
       </c>
       <c r="E335">
         <v>200</v>
@@ -11424,10 +11424,10 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C336" t="str">
-        <v>Malted Chocolate Americano</v>
+        <v>Horchata</v>
       </c>
       <c r="D336" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz) l Almond</v>
       </c>
       <c r="E336">
         <v>200</v>
@@ -11441,13 +11441,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C337" t="str">
-        <v>Malted Chocolate Americano</v>
+        <v>Horchata</v>
       </c>
       <c r="D337" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Large (16oz) l Oat</v>
       </c>
       <c r="E337">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="338">
@@ -11458,13 +11458,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C338" t="str">
-        <v>Malted Milk Protein Latte</v>
+        <v>Malted Chocolate Americano</v>
       </c>
       <c r="D338" t="str">
         <v>Iced Regular (12oz)</v>
       </c>
       <c r="E338">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row r="339">
@@ -11475,13 +11475,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C339" t="str">
-        <v>Malted Milk Protein Latte</v>
+        <v>Malted Chocolate Americano</v>
       </c>
       <c r="D339" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E339">
-        <v>240</v>
+        <v>210</v>
       </c>
     </row>
     <row r="340">
@@ -11492,7 +11492,7 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C340" t="str">
-        <v>Peanut Butter Protein Latte</v>
+        <v>Malted Milk Protein Latte</v>
       </c>
       <c r="D340" t="str">
         <v>Iced Regular (12oz)</v>
@@ -11509,7 +11509,7 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C341" t="str">
-        <v>Peanut Butter Protein Latte</v>
+        <v>Malted Milk Protein Latte</v>
       </c>
       <c r="D341" t="str">
         <v>Iced Large (16oz)</v>
@@ -11526,13 +11526,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C342" t="str">
-        <v>Salted Caramel Matcha</v>
+        <v>Peanut Butter Protein Latte</v>
       </c>
       <c r="D342" t="str">
         <v>Iced Regular (12oz)</v>
       </c>
       <c r="E342">
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row r="343">
@@ -11543,13 +11543,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C343" t="str">
-        <v>Salted Caramel Matcha</v>
+        <v>Peanut Butter Protein Latte</v>
       </c>
       <c r="D343" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E343">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="344">
@@ -11560,13 +11560,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C344" t="str">
-        <v>Salted Cream Matcha</v>
+        <v>Salted Caramel Matcha</v>
       </c>
       <c r="D344" t="str">
         <v>Iced Regular (12oz)</v>
       </c>
       <c r="E344">
-        <v>230</v>
+        <v>210</v>
       </c>
     </row>
     <row r="345">
@@ -11577,13 +11577,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C345" t="str">
-        <v>Salted Cream Matcha</v>
+        <v>Salted Caramel Matcha</v>
       </c>
       <c r="D345" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E345">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="346">
@@ -11594,7 +11594,7 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C346" t="str">
-        <v>Salted Dark Choc Protein Latte</v>
+        <v>Salted Cream Matcha</v>
       </c>
       <c r="D346" t="str">
         <v>Iced Regular (12oz)</v>
@@ -11611,7 +11611,7 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C347" t="str">
-        <v>Salted Dark Choc Protein Latte</v>
+        <v>Salted Cream Matcha</v>
       </c>
       <c r="D347" t="str">
         <v>Iced Large (16oz)</v>
@@ -11628,10 +11628,10 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C348" t="str">
-        <v>Salted Dark Chocolate</v>
+        <v>Salted Dark Choc Protein Latte</v>
       </c>
       <c r="D348" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E348">
         <v>230</v>
@@ -11645,10 +11645,10 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C349" t="str">
-        <v>Salted Honey Oat Latte</v>
+        <v>Salted Dark Choc Protein Latte</v>
       </c>
       <c r="D349" t="str">
-        <v>Iced Regular (12oz) l Dairy</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E349">
         <v>240</v>
@@ -11662,13 +11662,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C350" t="str">
-        <v>Salted Honey Oat Latte</v>
+        <v>Salted Dark Chocolate</v>
       </c>
       <c r="D350" t="str">
-        <v>Iced Regular (12oz) l Almond</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E350">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="351">
@@ -11682,7 +11682,7 @@
         <v>Salted Honey Oat Latte</v>
       </c>
       <c r="D351" t="str">
-        <v>Iced Regular (12oz) l Oat</v>
+        <v>Iced Regular (12oz) l Dairy</v>
       </c>
       <c r="E351">
         <v>240</v>
@@ -11699,10 +11699,10 @@
         <v>Salted Honey Oat Latte</v>
       </c>
       <c r="D352" t="str">
-        <v>Iced Large (16oz) l Dairy</v>
+        <v>Iced Regular (12oz) l Almond</v>
       </c>
       <c r="E352">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="353">
@@ -11716,10 +11716,10 @@
         <v>Salted Honey Oat Latte</v>
       </c>
       <c r="D353" t="str">
-        <v>Iced Large (16oz) l Almond</v>
+        <v>Iced Regular (12oz) l Oat</v>
       </c>
       <c r="E353">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="354">
@@ -11733,7 +11733,7 @@
         <v>Salted Honey Oat Latte</v>
       </c>
       <c r="D354" t="str">
-        <v>Iced Large (16oz) l Oat</v>
+        <v>Iced Large (16oz) l Dairy</v>
       </c>
       <c r="E354">
         <v>250</v>
@@ -11747,13 +11747,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C355" t="str">
-        <v>Shaken Coconut Cold Brew</v>
+        <v>Salted Honey Oat Latte</v>
       </c>
       <c r="D355" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Large (16oz) l Almond</v>
       </c>
       <c r="E355">
-        <v>240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="356">
@@ -11764,13 +11764,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C356" t="str">
-        <v>Shaken Creamy Lemonade</v>
+        <v>Salted Honey Oat Latte</v>
       </c>
       <c r="D356" t="str">
-        <v>Iced Large (16oz)</v>
+        <v>Iced Large (16oz) l Oat</v>
       </c>
       <c r="E356">
-        <v>190</v>
+        <v>250</v>
       </c>
     </row>
     <row r="357">
@@ -11781,13 +11781,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C357" t="str">
-        <v>Strawberry Cream Matcha</v>
+        <v>Shaken Coconut Cold Brew</v>
       </c>
       <c r="D357" t="str">
-        <v>Iced Regular (12oz)</v>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E357">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="358">
@@ -11798,13 +11798,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C358" t="str">
-        <v>Strawberry Cream Matcha</v>
+        <v>Shaken Creamy Lemonade</v>
       </c>
       <c r="D358" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E358">
-        <v>240</v>
+        <v>190</v>
       </c>
     </row>
     <row r="359">
@@ -11815,7 +11815,7 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C359" t="str">
-        <v>Strawberry Hojicha Latte</v>
+        <v>Strawberry Cream Matcha</v>
       </c>
       <c r="D359" t="str">
         <v>Iced Regular (12oz)</v>
@@ -11832,7 +11832,7 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C360" t="str">
-        <v>Strawberry Hojicha Latte</v>
+        <v>Strawberry Cream Matcha</v>
       </c>
       <c r="D360" t="str">
         <v>Iced Large (16oz)</v>
@@ -11849,13 +11849,13 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C361" t="str">
-        <v>Strawberry Milk</v>
+        <v>Strawberry Hojicha Latte</v>
       </c>
       <c r="D361" t="str">
         <v>Iced Regular (12oz)</v>
       </c>
       <c r="E361">
-        <v>190</v>
+        <v>230</v>
       </c>
     </row>
     <row r="362">
@@ -11866,47 +11866,47 @@
         <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C362" t="str">
-        <v>Strawberry Milk</v>
+        <v>Strawberry Hojicha Latte</v>
       </c>
       <c r="D362" t="str">
         <v>Iced Large (16oz)</v>
       </c>
       <c r="E362">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>SNACKS</v>
+        <v>ICED</v>
       </c>
       <c r="B363" t="str">
-        <v>11 DEL - SNACKS</v>
+        <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C363" t="str">
-        <v>Black &amp; White Bar</v>
+        <v>Strawberry Milk</v>
       </c>
       <c r="D363" t="str">
-        <v/>
+        <v>Iced Regular (12oz)</v>
       </c>
       <c r="E363">
-        <v>105</v>
+        <v>190</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>SNACKS</v>
+        <v>ICED</v>
       </c>
       <c r="B364" t="str">
-        <v>11 DEL - SNACKS</v>
+        <v>10 DEL - SIGNATURES</v>
       </c>
       <c r="C364" t="str">
-        <v>Calamansi Protein Bar</v>
+        <v>Strawberry Milk</v>
       </c>
       <c r="D364" t="str">
-        <v/>
+        <v>Iced Large (16oz)</v>
       </c>
       <c r="E364">
-        <v>105</v>
+        <v>200</v>
       </c>
     </row>
     <row r="365">
@@ -11917,13 +11917,13 @@
         <v>11 DEL - SNACKS</v>
       </c>
       <c r="C365" t="str">
-        <v>Chocolate Salt Bread</v>
+        <v>Black &amp; White Bar</v>
       </c>
       <c r="D365" t="str">
         <v/>
       </c>
       <c r="E365">
-        <v>85</v>
+        <v>105</v>
       </c>
     </row>
     <row r="366">
@@ -11934,13 +11934,13 @@
         <v>11 DEL - SNACKS</v>
       </c>
       <c r="C366" t="str">
-        <v>Corned Beef Pandesal</v>
+        <v>Calamansi Protein Bar</v>
       </c>
       <c r="D366" t="str">
         <v/>
       </c>
       <c r="E366">
-        <v>70</v>
+        <v>105</v>
       </c>
     </row>
     <row r="367">
@@ -11951,13 +11951,13 @@
         <v>11 DEL - SNACKS</v>
       </c>
       <c r="C367" t="str">
-        <v>Double Chocolate Chip Cookie</v>
+        <v>Chocolate Salt Bread</v>
       </c>
       <c r="D367" t="str">
         <v/>
       </c>
       <c r="E367">
-        <v>135</v>
+        <v>85</v>
       </c>
     </row>
     <row r="368">
@@ -11968,13 +11968,13 @@
         <v>11 DEL - SNACKS</v>
       </c>
       <c r="C368" t="str">
-        <v>Everything Dagel</v>
+        <v>Corned Beef Pandesal</v>
       </c>
       <c r="D368" t="str">
         <v/>
       </c>
       <c r="E368">
-        <v>165</v>
+        <v>70</v>
       </c>
     </row>
     <row r="369">
@@ -11985,13 +11985,13 @@
         <v>11 DEL - SNACKS</v>
       </c>
       <c r="C369" t="str">
-        <v>Ham Egg and Cheese Dagel</v>
+        <v>Double Chocolate Chip Cookie</v>
       </c>
       <c r="D369" t="str">
         <v/>
       </c>
       <c r="E369">
-        <v>190</v>
+        <v>135</v>
       </c>
     </row>
     <row r="370">
@@ -12002,13 +12002,13 @@
         <v>11 DEL - SNACKS</v>
       </c>
       <c r="C370" t="str">
-        <v>Oatmeal Crunch Protein Bar</v>
+        <v>Everything Dagel</v>
       </c>
       <c r="D370" t="str">
         <v/>
       </c>
       <c r="E370">
-        <v>105</v>
+        <v>165</v>
       </c>
     </row>
     <row r="371">
@@ -12019,13 +12019,13 @@
         <v>11 DEL - SNACKS</v>
       </c>
       <c r="C371" t="str">
-        <v>Oatmeal Protein Cookie</v>
+        <v>Ham Egg and Cheese Dagel</v>
       </c>
       <c r="D371" t="str">
         <v/>
       </c>
       <c r="E371">
-        <v>95</v>
+        <v>190</v>
       </c>
     </row>
     <row r="372">
@@ -12036,7 +12036,7 @@
         <v>11 DEL - SNACKS</v>
       </c>
       <c r="C372" t="str">
-        <v>Peanut Butter Monkey Bar</v>
+        <v>Oatmeal Crunch Protein Bar</v>
       </c>
       <c r="D372" t="str">
         <v/>
@@ -12053,13 +12053,13 @@
         <v>11 DEL - SNACKS</v>
       </c>
       <c r="C373" t="str">
-        <v>Salt Bread</v>
+        <v>Oatmeal Protein Cookie</v>
       </c>
       <c r="D373" t="str">
         <v/>
       </c>
       <c r="E373">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="374">
@@ -12070,13 +12070,13 @@
         <v>11 DEL - SNACKS</v>
       </c>
       <c r="C374" t="str">
-        <v>Spinach Mushroom Pandesal</v>
+        <v>Peanut Butter Monkey Bar</v>
       </c>
       <c r="D374" t="str">
         <v/>
       </c>
       <c r="E374">
-        <v>75</v>
+        <v>105</v>
       </c>
     </row>
     <row r="375">
@@ -12087,47 +12087,47 @@
         <v>11 DEL - SNACKS</v>
       </c>
       <c r="C375" t="str">
-        <v>Truffle Salt Bread</v>
+        <v>Salt Bread</v>
       </c>
       <c r="D375" t="str">
         <v/>
       </c>
       <c r="E375">
-        <v>105</v>
+        <v>80</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>MERCH</v>
+        <v>SNACKS</v>
       </c>
       <c r="B376" t="str">
-        <v>12 DEL - MERCH</v>
+        <v>11 DEL - SNACKS</v>
       </c>
       <c r="C376" t="str">
-        <v>Tumbler Add-On</v>
+        <v>Spinach Mushroom Pandesal</v>
       </c>
       <c r="D376" t="str">
-        <v>Set 1 (Straw + Rubber Stopper for Lid)</v>
+        <v/>
       </c>
       <c r="E376">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>MERCH</v>
+        <v>SNACKS</v>
       </c>
       <c r="B377" t="str">
-        <v>12 DEL - MERCH</v>
+        <v>11 DEL - SNACKS</v>
       </c>
       <c r="C377" t="str">
-        <v>Tumbler Add-On</v>
+        <v>Truffle Salt Bread</v>
       </c>
       <c r="D377" t="str">
-        <v>Set 2 (Silicone Boot + Handle)</v>
+        <v/>
       </c>
       <c r="E377">
-        <v>225</v>
+        <v>105</v>
       </c>
     </row>
     <row r="378">
@@ -12138,52 +12138,86 @@
         <v>12 DEL - MERCH</v>
       </c>
       <c r="C378" t="str">
-        <v>Tumbler Holiday Set</v>
+        <v>Tumbler Add-On</v>
       </c>
       <c r="D378" t="str">
-        <v>with extra straw</v>
+        <v>Set 1 (Straw + Rubber Stopper for Lid)</v>
       </c>
       <c r="E378">
-        <v>650</v>
+        <v>100</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>ADD ONS</v>
+        <v>MERCH</v>
       </c>
       <c r="B379" t="str">
-        <v>01 ADD ONS</v>
+        <v>12 DEL - MERCH</v>
       </c>
       <c r="C379" t="str">
-        <v>ADD ONS FOAM</v>
+        <v>Tumbler Add-On</v>
       </c>
       <c r="D379" t="str">
-        <v>Vanilla Foam</v>
+        <v>Set 2 (Silicone Boot + Handle)</v>
       </c>
       <c r="E379">
-        <v>40</v>
+        <v>225</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
+        <v>MERCH</v>
+      </c>
+      <c r="B380" t="str">
+        <v>12 DEL - MERCH</v>
+      </c>
+      <c r="C380" t="str">
+        <v>Tumbler Holiday Set</v>
+      </c>
+      <c r="D380" t="str">
+        <v>with extra straw</v>
+      </c>
+      <c r="E380">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
         <v>ADD ONS</v>
       </c>
-      <c r="B380" t="str">
+      <c r="B381" t="str">
+        <v>01 ADD ONS</v>
+      </c>
+      <c r="C381" t="str">
+        <v>ADD ONS FOAM</v>
+      </c>
+      <c r="D381" t="str">
+        <v>Vanilla Foam</v>
+      </c>
+      <c r="E381">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>ADD ONS</v>
+      </c>
+      <c r="B382" t="str">
         <v>08 DEL - ADD ONS</v>
       </c>
-      <c r="C380" t="str">
+      <c r="C382" t="str">
         <v>ADD ONS FOAM</v>
       </c>
-      <c r="D380" t="str">
+      <c r="D382" t="str">
         <v>Vanilla Foam</v>
       </c>
-      <c r="E380">
+      <c r="E382">
         <v>55</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E380"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E382"/>
   </ignoredErrors>
 </worksheet>
 </file>
